--- a/results/endesa-sentiment-2026-05-03.xlsx
+++ b/results/endesa-sentiment-2026-05-03.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="46" uniqueCount="45">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="46" uniqueCount="44">
   <si>
     <t>Metric</t>
   </si>
@@ -96,6 +96,35 @@
   </si>
   <si>
     <t>Collected At</t>
+  </si>
+  <si>
+    <t>AxVake</t>
+  </si>
+  <si>
+    <t>Cancelamento serviço prosegur</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Olá a todos
+Escrevo aqui no ambito de ter uma opinião e possiveis conselhos de como poderei proceder para cancelar da melhor forma o meu serviço da prosegur alarmes. Deixo aqui o contexto total para perceberem:
+Em setembro do ano passado decidi colocar um alarme da prosegur na obra da minha casa uma vez que foram lá roubar-me várias ferramentas. Liguei para o nº geral e apareceram 2 vendedores que me garantiram que era tudo possível e viável, mesmo estando a obra a decorrer obras, que seria su</t>
+  </si>
+  <si>
+    <t>https://www.reddit.com/r/portugal/comments/1sy5gip/cancelamento_servi%C3%A7o_prosegur/</t>
+  </si>
+  <si>
+    <t>portugal</t>
+  </si>
+  <si>
+    <t>2026-04-28T15:55:38.000Z</t>
+  </si>
+  <si>
+    <t>-5.000</t>
+  </si>
+  <si>
+    <t>Yes</t>
+  </si>
+  <si>
+    <t>2026-05-03T17:44:19.030Z</t>
   </si>
   <si>
     <t>Special_Chart2975</t>
@@ -112,9 +141,6 @@
     <t>https://www.reddit.com/r/portugal/comments/1skea7k/endesa_altera%C3%A7%C3%A3o_de_dados_sem_o_meu_conhecimento/</t>
   </si>
   <si>
-    <t>portugal</t>
-  </si>
-  <si>
     <t>2026-04-13T15:30:34.000Z</t>
   </si>
   <si>
@@ -122,35 +148,6 @@
   </si>
   <si>
     <t>No</t>
-  </si>
-  <si>
-    <t>2026-05-03T16:00:40.917Z</t>
-  </si>
-  <si>
-    <t>AxVake</t>
-  </si>
-  <si>
-    <t>Cancelamento serviço prosegur</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Olá a todos
-Escrevo aqui no ambito de ter uma opinião e possiveis conselhos de como poderei proceder para cancelar da melhor forma o meu serviço da prosegur alarmes. Deixo aqui o contexto total para perceberem:
-Em setembro do ano passado decidi colocar um alarme da prosegur na obra da minha casa uma vez que foram lá roubar-me várias ferramentas. Liguei para o nº geral e apareceram 2 vendedores que me garantiram que era tudo possível e viável, mesmo estando a obra a decorrer obras, que seria su</t>
-  </si>
-  <si>
-    <t>https://www.reddit.com/r/portugal/comments/1sy5gip/cancelamento_servi%C3%A7o_prosegur/</t>
-  </si>
-  <si>
-    <t>2026-04-28T15:55:38.000Z</t>
-  </si>
-  <si>
-    <t>-5.000</t>
-  </si>
-  <si>
-    <t>Yes</t>
-  </si>
-  <si>
-    <t>2026-05-03T16:00:40.919Z</t>
   </si>
 </sst>
 </file>
@@ -239,13 +236,13 @@
     <xf numFmtId="0" fontId="2" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -768,12 +765,12 @@
         <v>33</v>
       </c>
       <c r="G2" s="5">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H2" s="5">
-        <v>5</v>
-      </c>
-      <c r="I2" s="5" t="s">
+        <v>20</v>
+      </c>
+      <c r="I2" s="7" t="s">
         <v>34</v>
       </c>
       <c r="J2" s="5" t="s">
@@ -784,38 +781,38 @@
       </c>
     </row>
     <row r="3" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A3" s="7" t="s">
+      <c r="A3" s="8" t="s">
         <v>37</v>
       </c>
-      <c r="B3" s="7" t="s">
+      <c r="B3" s="8" t="s">
         <v>38</v>
       </c>
-      <c r="C3" s="7" t="s">
+      <c r="C3" s="8" t="s">
         <v>39</v>
       </c>
-      <c r="D3" s="8" t="s">
+      <c r="D3" s="9" t="s">
         <v>40</v>
       </c>
-      <c r="E3" s="7" t="s">
+      <c r="E3" s="8" t="s">
         <v>32</v>
       </c>
-      <c r="F3" s="7" t="s">
+      <c r="F3" s="8" t="s">
         <v>41</v>
       </c>
-      <c r="G3" s="7">
-        <v>2</v>
-      </c>
-      <c r="H3" s="7">
-        <v>20</v>
-      </c>
-      <c r="I3" s="9" t="s">
+      <c r="G3" s="8">
+        <v>1</v>
+      </c>
+      <c r="H3" s="8">
+        <v>5</v>
+      </c>
+      <c r="I3" s="8" t="s">
         <v>42</v>
       </c>
-      <c r="J3" s="7" t="s">
+      <c r="J3" s="8" t="s">
         <v>43</v>
       </c>
-      <c r="K3" s="7" t="s">
-        <v>44</v>
+      <c r="K3" s="8" t="s">
+        <v>36</v>
       </c>
     </row>
   </sheetData>

--- a/results/endesa-sentiment-2026-05-03.xlsx
+++ b/results/endesa-sentiment-2026-05-03.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="46" uniqueCount="44">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="46" uniqueCount="45">
   <si>
     <t>Metric</t>
   </si>
@@ -96,6 +96,35 @@
   </si>
   <si>
     <t>Collected At</t>
+  </si>
+  <si>
+    <t>Special_Chart2975</t>
+  </si>
+  <si>
+    <t>Endesa: alteração de dados sem o meu conhecimento</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Olá a todos. 
+Sou gerente de uma empresa e tenho contrato de energia com a Endesa. Após estar há 2 meses sem receber no e-mail habitual as faturas, e por necessidade de a enviar para a contabilidade, acabei por ligar para a Endesa para perceber o porquê de ainda não ter a fatura de março. Ao que me responderam que receberam em fevereiro um pedido via web de alteração de e-mail associado ao contrato, onde inclusive forneceram o meu CPE. 
+Somos uma micro-empresa familiar e não foi nenhum de nós </t>
+  </si>
+  <si>
+    <t>https://www.reddit.com/r/portugal/comments/1skea7k/endesa_altera%C3%A7%C3%A3o_de_dados_sem_o_meu_conhecimento/</t>
+  </si>
+  <si>
+    <t>portugal</t>
+  </si>
+  <si>
+    <t>2026-04-13T15:30:34.000Z</t>
+  </si>
+  <si>
+    <t>-1.000</t>
+  </si>
+  <si>
+    <t>No</t>
+  </si>
+  <si>
+    <t>2026-05-03T20:16:37.290Z</t>
   </si>
   <si>
     <t>AxVake</t>
@@ -112,9 +141,6 @@
     <t>https://www.reddit.com/r/portugal/comments/1sy5gip/cancelamento_servi%C3%A7o_prosegur/</t>
   </si>
   <si>
-    <t>portugal</t>
-  </si>
-  <si>
     <t>2026-04-28T15:55:38.000Z</t>
   </si>
   <si>
@@ -124,30 +150,7 @@
     <t>Yes</t>
   </si>
   <si>
-    <t>2026-05-03T17:44:19.030Z</t>
-  </si>
-  <si>
-    <t>Special_Chart2975</t>
-  </si>
-  <si>
-    <t>Endesa: alteração de dados sem o meu conhecimento</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Olá a todos. 
-Sou gerente de uma empresa e tenho contrato de energia com a Endesa. Após estar há 2 meses sem receber no e-mail habitual as faturas, e por necessidade de a enviar para a contabilidade, acabei por ligar para a Endesa para perceber o porquê de ainda não ter a fatura de março. Ao que me responderam que receberam em fevereiro um pedido via web de alteração de e-mail associado ao contrato, onde inclusive forneceram o meu CPE. 
-Somos uma micro-empresa familiar e não foi nenhum de nós </t>
-  </si>
-  <si>
-    <t>https://www.reddit.com/r/portugal/comments/1skea7k/endesa_altera%C3%A7%C3%A3o_de_dados_sem_o_meu_conhecimento/</t>
-  </si>
-  <si>
-    <t>2026-04-13T15:30:34.000Z</t>
-  </si>
-  <si>
-    <t>-1.000</t>
-  </si>
-  <si>
-    <t>No</t>
+    <t>2026-05-03T20:16:37.291Z</t>
   </si>
 </sst>
 </file>
@@ -236,13 +239,13 @@
     <xf numFmtId="0" fontId="2" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -765,12 +768,12 @@
         <v>33</v>
       </c>
       <c r="G2" s="5">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H2" s="5">
-        <v>20</v>
-      </c>
-      <c r="I2" s="7" t="s">
+        <v>5</v>
+      </c>
+      <c r="I2" s="5" t="s">
         <v>34</v>
       </c>
       <c r="J2" s="5" t="s">
@@ -781,38 +784,38 @@
       </c>
     </row>
     <row r="3" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A3" s="8" t="s">
+      <c r="A3" s="7" t="s">
         <v>37</v>
       </c>
-      <c r="B3" s="8" t="s">
+      <c r="B3" s="7" t="s">
         <v>38</v>
       </c>
-      <c r="C3" s="8" t="s">
+      <c r="C3" s="7" t="s">
         <v>39</v>
       </c>
-      <c r="D3" s="9" t="s">
+      <c r="D3" s="8" t="s">
         <v>40</v>
       </c>
-      <c r="E3" s="8" t="s">
+      <c r="E3" s="7" t="s">
         <v>32</v>
       </c>
-      <c r="F3" s="8" t="s">
+      <c r="F3" s="7" t="s">
         <v>41</v>
       </c>
-      <c r="G3" s="8">
-        <v>1</v>
-      </c>
-      <c r="H3" s="8">
-        <v>5</v>
-      </c>
-      <c r="I3" s="8" t="s">
+      <c r="G3" s="7">
+        <v>2</v>
+      </c>
+      <c r="H3" s="7">
+        <v>20</v>
+      </c>
+      <c r="I3" s="9" t="s">
         <v>42</v>
       </c>
-      <c r="J3" s="8" t="s">
+      <c r="J3" s="7" t="s">
         <v>43</v>
       </c>
-      <c r="K3" s="8" t="s">
-        <v>36</v>
+      <c r="K3" s="7" t="s">
+        <v>44</v>
       </c>
     </row>
   </sheetData>

--- a/results/endesa-sentiment-2026-05-03.xlsx
+++ b/results/endesa-sentiment-2026-05-03.xlsx
@@ -5,14 +5,14 @@
   <workbookPr defaultThemeVersion="164011" filterPrivacy="1"/>
   <sheets>
     <sheet sheetId="1" name="Summary" state="visible" r:id="rId4"/>
-    <sheet sheetId="2" name="Negative Posts" state="visible" r:id="rId5"/>
+    <sheet sheetId="2" name="All Posts" state="visible" r:id="rId5"/>
   </sheets>
   <calcPr calcId="171027"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="46" uniqueCount="45">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="69" uniqueCount="60">
   <si>
     <t>Metric</t>
   </si>
@@ -44,7 +44,7 @@
     <t>Negative %</t>
   </si>
   <si>
-    <t>50.0%</t>
+    <t>75.0%</t>
   </si>
   <si>
     <t>Average Sentiment Score</t>
@@ -89,6 +89,9 @@
     <t>Comments</t>
   </si>
   <si>
+    <t>Sentiment</t>
+  </si>
+  <si>
     <t>Sentiment Score</t>
   </si>
   <si>
@@ -96,6 +99,89 @@
   </si>
   <si>
     <t>Collected At</t>
+  </si>
+  <si>
+    <t>BeautifulEducation91</t>
+  </si>
+  <si>
+    <t>Dificuldade no Contrato de Eletricidade</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Olá Portugal!
+Decidi arrendar um apartamento e ia mudar-me amanhã (domingo, dia 3).  
+A data de início do contrato foi ontem dia 1, mas deram-me a chave na última segunda-feira, assim como o certificado energético e assinatura do contrato de arrendamento, para poder começar a fazer algumas mudanças e tratar dos contratos.  
+A EPAL deu alguma luta, mas já foi; a DIGI foi muito intuitiva e já estou só a aguardar o técnico ir lá a casa e agora é o tema da eletricidade.  
+Estive de segunda a quarta</t>
+  </si>
+  <si>
+    <t>https://www.reddit.com/r/portugal/comments/1t1kmh9/dificuldade_no_contrato_de_eletricidade/</t>
+  </si>
+  <si>
+    <t>portugal</t>
+  </si>
+  <si>
+    <t>2026-05-02T08:57:51.000Z</t>
+  </si>
+  <si>
+    <t>Positive</t>
+  </si>
+  <si>
+    <t>2.000</t>
+  </si>
+  <si>
+    <t>No</t>
+  </si>
+  <si>
+    <t>2026-05-03T20:30:53.135Z</t>
+  </si>
+  <si>
+    <t>AxVake</t>
+  </si>
+  <si>
+    <t>Cancelamento serviço prosegur</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Olá a todos
+Escrevo aqui no ambito de ter uma opinião e possiveis conselhos de como poderei proceder para cancelar da melhor forma o meu serviço da prosegur alarmes. Deixo aqui o contexto total para perceberem:
+Em setembro do ano passado decidi colocar um alarme da prosegur na obra da minha casa uma vez que foram lá roubar-me várias ferramentas. Liguei para o nº geral e apareceram 2 vendedores que me garantiram que era tudo possível e viável, mesmo estando a obra a decorrer obras, que seria su</t>
+  </si>
+  <si>
+    <t>https://www.reddit.com/r/portugal/comments/1sy5gip/cancelamento_servi%C3%A7o_prosegur/</t>
+  </si>
+  <si>
+    <t>2026-04-28T15:55:38.000Z</t>
+  </si>
+  <si>
+    <t>Negative</t>
+  </si>
+  <si>
+    <t>-5.000</t>
+  </si>
+  <si>
+    <t>Yes</t>
+  </si>
+  <si>
+    <t>FastStranger3827</t>
+  </si>
+  <si>
+    <t>Endesa cobrou-me 200€ de gás por causa de "estimativas" durante quase 1 ano - isto é normal?</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Boas,
+Queria saber se isto já aconteceu a alguém.
+Tenho gás na Endesa e durante meses recebi faturas de 20€ ou 30€. Sempre paguei tudo normalmente. Agora recebi uma fatura de quase 200€ e dizem que é um acerto porque as anteriores eram estimativas.
+Disseram que a empresa que faz a leitura do contador não foi lá durante quase 10 meses, por isso andaram a estimar o consumo. Agora que fizeram uma leitura real dizem que tenho de pagar a diferença.
+A minha dúvida é: isto é normal?
+Se não foram f</t>
+  </si>
+  <si>
+    <t>https://www.reddit.com/r/portugal/comments/1sned4s/endesa_cobroume_200_de_g%C3%A1s_por_causa_de/</t>
+  </si>
+  <si>
+    <t>2026-04-16T19:50:42.000Z</t>
+  </si>
+  <si>
+    <t>0.000</t>
   </si>
   <si>
     <t>Special_Chart2975</t>
@@ -112,52 +198,20 @@
     <t>https://www.reddit.com/r/portugal/comments/1skea7k/endesa_altera%C3%A7%C3%A3o_de_dados_sem_o_meu_conhecimento/</t>
   </si>
   <si>
-    <t>portugal</t>
-  </si>
-  <si>
     <t>2026-04-13T15:30:34.000Z</t>
   </si>
   <si>
     <t>-1.000</t>
   </si>
   <si>
-    <t>No</t>
-  </si>
-  <si>
-    <t>2026-05-03T20:16:37.290Z</t>
-  </si>
-  <si>
-    <t>AxVake</t>
-  </si>
-  <si>
-    <t>Cancelamento serviço prosegur</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Olá a todos
-Escrevo aqui no ambito de ter uma opinião e possiveis conselhos de como poderei proceder para cancelar da melhor forma o meu serviço da prosegur alarmes. Deixo aqui o contexto total para perceberem:
-Em setembro do ano passado decidi colocar um alarme da prosegur na obra da minha casa uma vez que foram lá roubar-me várias ferramentas. Liguei para o nº geral e apareceram 2 vendedores que me garantiram que era tudo possível e viável, mesmo estando a obra a decorrer obras, que seria su</t>
-  </si>
-  <si>
-    <t>https://www.reddit.com/r/portugal/comments/1sy5gip/cancelamento_servi%C3%A7o_prosegur/</t>
-  </si>
-  <si>
-    <t>2026-04-28T15:55:38.000Z</t>
-  </si>
-  <si>
-    <t>-5.000</t>
-  </si>
-  <si>
-    <t>Yes</t>
-  </si>
-  <si>
-    <t>2026-05-03T20:16:37.291Z</t>
+    <t>2026-05-03T20:30:53.136Z</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
-  <fonts count="4" x14ac:knownFonts="1">
+  <fonts count="5" x14ac:knownFonts="1">
     <font>
       <color theme="1"/>
       <family val="2"/>
@@ -172,6 +226,10 @@
     <font>
       <u/>
       <color rgb="FF0563C1"/>
+    </font>
+    <font>
+      <b/>
+      <color rgb="FF27AE60"/>
     </font>
     <font>
       <b/>
@@ -202,7 +260,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFC0392B"/>
+        <fgColor rgb="FFF0FFF0"/>
       </patternFill>
     </fill>
     <fill>
@@ -223,15 +281,24 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="10">
+  <cellXfs count="11">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="0" fontId="1" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="6" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
@@ -239,13 +306,7 @@
     <xf numFmtId="0" fontId="2" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -631,7 +692,7 @@
         <v>6</v>
       </c>
       <c r="B5" s="3">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="6" spans="1:2" x14ac:dyDescent="0.25">
@@ -647,7 +708,7 @@
         <v>8</v>
       </c>
       <c r="B7" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="8" spans="1:2" x14ac:dyDescent="0.25">
@@ -698,7 +759,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:K3"/>
+  <dimension ref="A1:L5"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="18" customWidth="1"/>
@@ -708,12 +769,13 @@
     <col min="5" max="5" width="14" customWidth="1"/>
     <col min="6" max="6" width="20" customWidth="1"/>
     <col min="7" max="8" width="10" customWidth="1"/>
-    <col min="9" max="9" width="16" customWidth="1"/>
-    <col min="10" max="10" width="14" customWidth="1"/>
-    <col min="11" max="11" width="22" customWidth="1"/>
+    <col min="9" max="9" width="12" customWidth="1"/>
+    <col min="10" max="10" width="16" customWidth="1"/>
+    <col min="11" max="11" width="14" customWidth="1"/>
+    <col min="12" max="12" width="22" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" ht="30" customHeight="1" spans="1:11" s="4" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="1" ht="30" customHeight="1" spans="1:12" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1" s="4" t="s">
         <v>17</v>
       </c>
@@ -747,82 +809,169 @@
       <c r="K1" s="4" t="s">
         <v>27</v>
       </c>
-    </row>
-    <row r="2" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="L1" s="4" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="2" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A2" s="5" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="B2" s="5" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="C2" s="5" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="D2" s="6" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="E2" s="5" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="F2" s="5" t="s">
+        <v>34</v>
+      </c>
+      <c r="G2" s="5">
+        <v>3</v>
+      </c>
+      <c r="H2" s="5">
+        <v>9</v>
+      </c>
+      <c r="I2" s="7" t="s">
+        <v>35</v>
+      </c>
+      <c r="J2" s="5" t="s">
+        <v>36</v>
+      </c>
+      <c r="K2" s="5" t="s">
+        <v>37</v>
+      </c>
+      <c r="L2" s="5" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="3" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A3" s="8" t="s">
+        <v>39</v>
+      </c>
+      <c r="B3" s="8" t="s">
+        <v>40</v>
+      </c>
+      <c r="C3" s="8" t="s">
+        <v>41</v>
+      </c>
+      <c r="D3" s="9" t="s">
+        <v>42</v>
+      </c>
+      <c r="E3" s="8" t="s">
         <v>33</v>
       </c>
-      <c r="G2" s="5">
+      <c r="F3" s="8" t="s">
+        <v>43</v>
+      </c>
+      <c r="G3" s="8">
+        <v>3</v>
+      </c>
+      <c r="H3" s="8">
+        <v>20</v>
+      </c>
+      <c r="I3" s="10" t="s">
+        <v>44</v>
+      </c>
+      <c r="J3" s="8" t="s">
+        <v>45</v>
+      </c>
+      <c r="K3" s="8" t="s">
+        <v>46</v>
+      </c>
+      <c r="L3" s="8" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="4" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A4" s="8" t="s">
+        <v>47</v>
+      </c>
+      <c r="B4" s="8" t="s">
+        <v>48</v>
+      </c>
+      <c r="C4" s="8" t="s">
+        <v>49</v>
+      </c>
+      <c r="D4" s="9" t="s">
+        <v>50</v>
+      </c>
+      <c r="E4" s="8" t="s">
+        <v>33</v>
+      </c>
+      <c r="F4" s="8" t="s">
+        <v>51</v>
+      </c>
+      <c r="G4" s="8">
+        <v>0</v>
+      </c>
+      <c r="H4" s="8">
+        <v>77</v>
+      </c>
+      <c r="I4" s="10" t="s">
+        <v>44</v>
+      </c>
+      <c r="J4" s="8" t="s">
+        <v>52</v>
+      </c>
+      <c r="K4" s="8" t="s">
+        <v>46</v>
+      </c>
+      <c r="L4" s="8" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="5" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A5" s="8" t="s">
+        <v>53</v>
+      </c>
+      <c r="B5" s="8" t="s">
+        <v>54</v>
+      </c>
+      <c r="C5" s="8" t="s">
+        <v>55</v>
+      </c>
+      <c r="D5" s="9" t="s">
+        <v>56</v>
+      </c>
+      <c r="E5" s="8" t="s">
+        <v>33</v>
+      </c>
+      <c r="F5" s="8" t="s">
+        <v>57</v>
+      </c>
+      <c r="G5" s="8">
         <v>1</v>
       </c>
-      <c r="H2" s="5">
+      <c r="H5" s="8">
         <v>5</v>
       </c>
-      <c r="I2" s="5" t="s">
-        <v>34</v>
-      </c>
-      <c r="J2" s="5" t="s">
-        <v>35</v>
-      </c>
-      <c r="K2" s="5" t="s">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="3" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A3" s="7" t="s">
+      <c r="I5" s="10" t="s">
+        <v>44</v>
+      </c>
+      <c r="J5" s="8" t="s">
+        <v>58</v>
+      </c>
+      <c r="K5" s="8" t="s">
         <v>37</v>
       </c>
-      <c r="B3" s="7" t="s">
-        <v>38</v>
-      </c>
-      <c r="C3" s="7" t="s">
-        <v>39</v>
-      </c>
-      <c r="D3" s="8" t="s">
-        <v>40</v>
-      </c>
-      <c r="E3" s="7" t="s">
-        <v>32</v>
-      </c>
-      <c r="F3" s="7" t="s">
-        <v>41</v>
-      </c>
-      <c r="G3" s="7">
-        <v>2</v>
-      </c>
-      <c r="H3" s="7">
-        <v>20</v>
-      </c>
-      <c r="I3" s="9" t="s">
-        <v>42</v>
-      </c>
-      <c r="J3" s="7" t="s">
-        <v>43</v>
-      </c>
-      <c r="K3" s="7" t="s">
-        <v>44</v>
+      <c r="L5" s="8" t="s">
+        <v>59</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:K1"/>
+  <autoFilter ref="A1:L1"/>
   <hyperlinks>
     <hyperlink ref="D2" r:id="rId1"/>
     <hyperlink ref="D3" r:id="rId2"/>
+    <hyperlink ref="D4" r:id="rId3"/>
+    <hyperlink ref="D5" r:id="rId4"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>

--- a/results/endesa-sentiment-2026-05-03.xlsx
+++ b/results/endesa-sentiment-2026-05-03.xlsx
@@ -101,66 +101,6 @@
     <t>Collected At</t>
   </si>
   <si>
-    <t>BeautifulEducation91</t>
-  </si>
-  <si>
-    <t>Dificuldade no Contrato de Eletricidade</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Olá Portugal!
-Decidi arrendar um apartamento e ia mudar-me amanhã (domingo, dia 3).  
-A data de início do contrato foi ontem dia 1, mas deram-me a chave na última segunda-feira, assim como o certificado energético e assinatura do contrato de arrendamento, para poder começar a fazer algumas mudanças e tratar dos contratos.  
-A EPAL deu alguma luta, mas já foi; a DIGI foi muito intuitiva e já estou só a aguardar o técnico ir lá a casa e agora é o tema da eletricidade.  
-Estive de segunda a quarta</t>
-  </si>
-  <si>
-    <t>https://www.reddit.com/r/portugal/comments/1t1kmh9/dificuldade_no_contrato_de_eletricidade/</t>
-  </si>
-  <si>
-    <t>portugal</t>
-  </si>
-  <si>
-    <t>2026-05-02T08:57:51.000Z</t>
-  </si>
-  <si>
-    <t>Positive</t>
-  </si>
-  <si>
-    <t>2.000</t>
-  </si>
-  <si>
-    <t>No</t>
-  </si>
-  <si>
-    <t>2026-05-03T20:30:53.135Z</t>
-  </si>
-  <si>
-    <t>AxVake</t>
-  </si>
-  <si>
-    <t>Cancelamento serviço prosegur</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Olá a todos
-Escrevo aqui no ambito de ter uma opinião e possiveis conselhos de como poderei proceder para cancelar da melhor forma o meu serviço da prosegur alarmes. Deixo aqui o contexto total para perceberem:
-Em setembro do ano passado decidi colocar um alarme da prosegur na obra da minha casa uma vez que foram lá roubar-me várias ferramentas. Liguei para o nº geral e apareceram 2 vendedores que me garantiram que era tudo possível e viável, mesmo estando a obra a decorrer obras, que seria su</t>
-  </si>
-  <si>
-    <t>https://www.reddit.com/r/portugal/comments/1sy5gip/cancelamento_servi%C3%A7o_prosegur/</t>
-  </si>
-  <si>
-    <t>2026-04-28T15:55:38.000Z</t>
-  </si>
-  <si>
-    <t>Negative</t>
-  </si>
-  <si>
-    <t>-5.000</t>
-  </si>
-  <si>
-    <t>Yes</t>
-  </si>
-  <si>
     <t>FastStranger3827</t>
   </si>
   <si>
@@ -178,10 +118,22 @@
     <t>https://www.reddit.com/r/portugal/comments/1sned4s/endesa_cobroume_200_de_g%C3%A1s_por_causa_de/</t>
   </si>
   <si>
+    <t>portugal</t>
+  </si>
+  <si>
     <t>2026-04-16T19:50:42.000Z</t>
   </si>
   <si>
+    <t>Negative</t>
+  </si>
+  <si>
     <t>0.000</t>
+  </si>
+  <si>
+    <t>Yes</t>
+  </si>
+  <si>
+    <t>2026-05-03T20:32:04.386Z</t>
   </si>
   <si>
     <t>Special_Chart2975</t>
@@ -204,7 +156,55 @@
     <t>-1.000</t>
   </si>
   <si>
-    <t>2026-05-03T20:30:53.136Z</t>
+    <t>No</t>
+  </si>
+  <si>
+    <t>2026-05-03T20:32:04.387Z</t>
+  </si>
+  <si>
+    <t>BeautifulEducation91</t>
+  </si>
+  <si>
+    <t>Dificuldade no Contrato de Eletricidade</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Olá Portugal!
+Decidi arrendar um apartamento e ia mudar-me amanhã (domingo, dia 3).  
+A data de início do contrato foi ontem dia 1, mas deram-me a chave na última segunda-feira, assim como o certificado energético e assinatura do contrato de arrendamento, para poder começar a fazer algumas mudanças e tratar dos contratos.  
+A EPAL deu alguma luta, mas já foi; a DIGI foi muito intuitiva e já estou só a aguardar o técnico ir lá a casa e agora é o tema da eletricidade.  
+Estive de segunda a quarta</t>
+  </si>
+  <si>
+    <t>https://www.reddit.com/r/portugal/comments/1t1kmh9/dificuldade_no_contrato_de_eletricidade/</t>
+  </si>
+  <si>
+    <t>2026-05-02T08:57:51.000Z</t>
+  </si>
+  <si>
+    <t>Positive</t>
+  </si>
+  <si>
+    <t>2.000</t>
+  </si>
+  <si>
+    <t>AxVake</t>
+  </si>
+  <si>
+    <t>Cancelamento serviço prosegur</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Olá a todos
+Escrevo aqui no ambito de ter uma opinião e possiveis conselhos de como poderei proceder para cancelar da melhor forma o meu serviço da prosegur alarmes. Deixo aqui o contexto total para perceberem:
+Em setembro do ano passado decidi colocar um alarme da prosegur na obra da minha casa uma vez que foram lá roubar-me várias ferramentas. Liguei para o nº geral e apareceram 2 vendedores que me garantiram que era tudo possível e viável, mesmo estando a obra a decorrer obras, que seria su</t>
+  </si>
+  <si>
+    <t>https://www.reddit.com/r/portugal/comments/1sy5gip/cancelamento_servi%C3%A7o_prosegur/</t>
+  </si>
+  <si>
+    <t>2026-04-28T15:55:38.000Z</t>
+  </si>
+  <si>
+    <t>-5.000</t>
   </si>
 </sst>
 </file>
@@ -229,11 +229,11 @@
     </font>
     <font>
       <b/>
-      <color rgb="FF27AE60"/>
+      <color rgb="FFCC0000"/>
     </font>
     <font>
       <b/>
-      <color rgb="FFCC0000"/>
+      <color rgb="FF27AE60"/>
     </font>
   </fonts>
   <fills count="7">
@@ -260,12 +260,12 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFF0FFF0"/>
+        <fgColor rgb="FFFFF5F5"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFF5F5"/>
+        <fgColor rgb="FFF0FFF0"/>
       </patternFill>
     </fill>
   </fills>
@@ -833,10 +833,10 @@
         <v>34</v>
       </c>
       <c r="G2" s="5">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="H2" s="5">
-        <v>9</v>
+        <v>77</v>
       </c>
       <c r="I2" s="7" t="s">
         <v>35</v>
@@ -852,41 +852,41 @@
       </c>
     </row>
     <row r="3" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A3" s="8" t="s">
+      <c r="A3" s="5" t="s">
         <v>39</v>
       </c>
-      <c r="B3" s="8" t="s">
+      <c r="B3" s="5" t="s">
         <v>40</v>
       </c>
-      <c r="C3" s="8" t="s">
+      <c r="C3" s="5" t="s">
         <v>41</v>
       </c>
-      <c r="D3" s="9" t="s">
+      <c r="D3" s="6" t="s">
         <v>42</v>
       </c>
-      <c r="E3" s="8" t="s">
+      <c r="E3" s="5" t="s">
         <v>33</v>
       </c>
-      <c r="F3" s="8" t="s">
+      <c r="F3" s="5" t="s">
         <v>43</v>
       </c>
-      <c r="G3" s="8">
-        <v>3</v>
-      </c>
-      <c r="H3" s="8">
-        <v>20</v>
-      </c>
-      <c r="I3" s="10" t="s">
+      <c r="G3" s="5">
+        <v>1</v>
+      </c>
+      <c r="H3" s="5">
+        <v>5</v>
+      </c>
+      <c r="I3" s="7" t="s">
+        <v>35</v>
+      </c>
+      <c r="J3" s="5" t="s">
         <v>44</v>
       </c>
-      <c r="J3" s="8" t="s">
+      <c r="K3" s="5" t="s">
         <v>45</v>
       </c>
-      <c r="K3" s="8" t="s">
+      <c r="L3" s="5" t="s">
         <v>46</v>
-      </c>
-      <c r="L3" s="8" t="s">
-        <v>38</v>
       </c>
     </row>
     <row r="4" spans="1:12" x14ac:dyDescent="0.25">
@@ -909,60 +909,60 @@
         <v>51</v>
       </c>
       <c r="G4" s="8">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="H4" s="8">
-        <v>77</v>
+        <v>9</v>
       </c>
       <c r="I4" s="10" t="s">
-        <v>44</v>
+        <v>52</v>
       </c>
       <c r="J4" s="8" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="K4" s="8" t="s">
+        <v>45</v>
+      </c>
+      <c r="L4" s="8" t="s">
         <v>46</v>
       </c>
-      <c r="L4" s="8" t="s">
-        <v>38</v>
-      </c>
     </row>
     <row r="5" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A5" s="8" t="s">
-        <v>53</v>
-      </c>
-      <c r="B5" s="8" t="s">
+      <c r="A5" s="5" t="s">
         <v>54</v>
       </c>
-      <c r="C5" s="8" t="s">
+      <c r="B5" s="5" t="s">
         <v>55</v>
       </c>
-      <c r="D5" s="9" t="s">
+      <c r="C5" s="5" t="s">
         <v>56</v>
       </c>
-      <c r="E5" s="8" t="s">
+      <c r="D5" s="6" t="s">
+        <v>57</v>
+      </c>
+      <c r="E5" s="5" t="s">
         <v>33</v>
       </c>
-      <c r="F5" s="8" t="s">
-        <v>57</v>
-      </c>
-      <c r="G5" s="8">
-        <v>1</v>
-      </c>
-      <c r="H5" s="8">
-        <v>5</v>
-      </c>
-      <c r="I5" s="10" t="s">
-        <v>44</v>
-      </c>
-      <c r="J5" s="8" t="s">
+      <c r="F5" s="5" t="s">
         <v>58</v>
       </c>
-      <c r="K5" s="8" t="s">
+      <c r="G5" s="5">
+        <v>4</v>
+      </c>
+      <c r="H5" s="5">
+        <v>20</v>
+      </c>
+      <c r="I5" s="7" t="s">
+        <v>35</v>
+      </c>
+      <c r="J5" s="5" t="s">
+        <v>59</v>
+      </c>
+      <c r="K5" s="5" t="s">
         <v>37</v>
       </c>
-      <c r="L5" s="8" t="s">
-        <v>59</v>
+      <c r="L5" s="5" t="s">
+        <v>46</v>
       </c>
     </row>
   </sheetData>
